--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="89">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -67,58 +70,199 @@
     <t>2026-05-12</t>
   </si>
   <si>
+    <t>2026-05-18</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-26</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-05-28</t>
+  </si>
+  <si>
+    <t>2026-05-29</t>
+  </si>
+  <si>
+    <t>1907 О5 Пловдив</t>
+  </si>
+  <si>
+    <t>1119 Асеновград</t>
+  </si>
+  <si>
+    <t>1130 Пловдив Кукленско шосе</t>
+  </si>
+  <si>
+    <t>1106 Пловдив В. Априлов</t>
+  </si>
+  <si>
     <t>АУ2</t>
   </si>
   <si>
     <t>АУ10</t>
   </si>
   <si>
+    <t>АУ6</t>
+  </si>
+  <si>
     <t>АУ1</t>
   </si>
   <si>
-    <t>АУ6</t>
-  </si>
-  <si>
     <t>АУ4</t>
   </si>
   <si>
+    <t>АУ3</t>
+  </si>
+  <si>
+    <t>АУ5</t>
+  </si>
+  <si>
+    <t>АУ9</t>
+  </si>
+  <si>
     <t>78970151027720104</t>
   </si>
   <si>
     <t>78970151027720187</t>
   </si>
   <si>
+    <t>78970151027720146</t>
+  </si>
+  <si>
     <t>78970151027720096</t>
   </si>
   <si>
-    <t>78970151027720146</t>
-  </si>
-  <si>
     <t>78970151027720120</t>
   </si>
   <si>
+    <t>78970151027720112</t>
+  </si>
+  <si>
+    <t>78970151027720138</t>
+  </si>
+  <si>
+    <t>78970151027720179</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>08:54</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>11:26</t>
-  </si>
-  <si>
-    <t>11:36</t>
-  </si>
-  <si>
-    <t>13:11</t>
+    <t>10L ADPLUS DIESEL ADDITIVE</t>
+  </si>
+  <si>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>08:53:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
+    <t>15:29:00</t>
+  </si>
+  <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
+    <t>11:26:00</t>
+  </si>
+  <si>
+    <t>13:11:00</t>
+  </si>
+  <si>
+    <t>15:44:00</t>
+  </si>
+  <si>
+    <t>15:46:00</t>
+  </si>
+  <si>
+    <t>08:33:00</t>
+  </si>
+  <si>
+    <t>16:13:00</t>
+  </si>
+  <si>
+    <t>10:17:00</t>
+  </si>
+  <si>
+    <t>12:03:00</t>
+  </si>
+  <si>
+    <t>12:41:00</t>
+  </si>
+  <si>
+    <t>08:07:00</t>
+  </si>
+  <si>
+    <t>10:44:00</t>
+  </si>
+  <si>
+    <t>10:48:00</t>
+  </si>
+  <si>
+    <t>08:14:00</t>
+  </si>
+  <si>
+    <t>3231549883 3231549883</t>
+  </si>
+  <si>
+    <t>3231613643 3231613643</t>
+  </si>
+  <si>
+    <t>3231738330 3231738330</t>
+  </si>
+  <si>
+    <t>3231774697 3231774697</t>
+  </si>
+  <si>
+    <t>3231774987 3231774987</t>
+  </si>
+  <si>
+    <t>3231777447 3231777447</t>
+  </si>
+  <si>
+    <t>3232064241 3232064241</t>
+  </si>
+  <si>
+    <t>3232204387 3232204387</t>
+  </si>
+  <si>
+    <t>3232175375 3232175375</t>
+  </si>
+  <si>
+    <t>3232206110 3232206110</t>
+  </si>
+  <si>
+    <t>3232432230 3232432230</t>
+  </si>
+  <si>
+    <t>3232482958 3232482958</t>
+  </si>
+  <si>
+    <t>3232484404 3232484404</t>
+  </si>
+  <si>
+    <t>3232530303 3232530303</t>
+  </si>
+  <si>
+    <t>3232525785 3232525785</t>
+  </si>
+  <si>
+    <t>3232530880 3232530880</t>
+  </si>
+  <si>
+    <t>3232573014 3232573014</t>
   </si>
   <si>
     <t>Общи литри по продукт / АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ</t>
@@ -542,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -551,16 +695,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -600,344 +745,869 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1907</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F2">
         <v>28</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2">
         <v>1.49</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>41.72</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.53</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>42.84</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
+      <c r="L2" t="s">
+        <v>49</v>
       </c>
       <c r="M2">
-        <v>145851</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1907</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F3">
         <v>19.6</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3">
         <v>1.49</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>29.2</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.53</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>29.99</v>
       </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
+      <c r="L3" t="s">
+        <v>50</v>
       </c>
       <c r="M3">
-        <v>146186</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1907</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F4">
         <v>47.15</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4">
         <v>1.75</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>82.51000000000001</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.79</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>84.40000000000001</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5">
+        <v>82.08</v>
+      </c>
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5">
+        <v>1.75</v>
+      </c>
+      <c r="I5" s="1">
+        <v>143.64</v>
+      </c>
+      <c r="J5">
+        <v>1.79</v>
+      </c>
+      <c r="K5" s="1">
+        <v>146.92</v>
+      </c>
+      <c r="L5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
         <v>31</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>147044</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1907</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="1">
+        <v>119.98</v>
+      </c>
+      <c r="J6">
+        <v>1.54</v>
+      </c>
+      <c r="K6" s="1">
+        <v>123.18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="H5">
-        <v>119.98</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="J5">
-        <v>123.18</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="C7" t="s">
         <v>32</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>147269</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6">
-        <v>1907</v>
-      </c>
-      <c r="C6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F6">
-        <v>82.08</v>
-      </c>
-      <c r="G6" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="H6">
-        <v>143.64</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1.79</v>
-      </c>
-      <c r="J6">
-        <v>146.92</v>
-      </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>147274</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7">
-        <v>1907</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F7">
         <v>55</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7">
         <v>1.75</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>96.25</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.79</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>98.45</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8">
+        <v>81.01000000000001</v>
+      </c>
+      <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8">
+        <v>1.7</v>
+      </c>
+      <c r="I8" s="1">
+        <v>137.72</v>
+      </c>
+      <c r="J8">
+        <v>1.74</v>
+      </c>
+      <c r="K8" s="1">
+        <v>140.96</v>
+      </c>
+      <c r="L8" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9">
+        <v>85</v>
+      </c>
+      <c r="G9" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9">
+        <v>1.71</v>
+      </c>
+      <c r="I9" s="1">
+        <v>145.35</v>
+      </c>
+      <c r="J9">
+        <v>1.75</v>
+      </c>
+      <c r="K9" s="1">
+        <v>148.75</v>
+      </c>
+      <c r="L9" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>22.86</v>
+      </c>
+      <c r="G10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H10">
+        <v>1.71</v>
+      </c>
+      <c r="I10" s="1">
+        <v>39.09</v>
+      </c>
+      <c r="J10">
+        <v>1.75</v>
+      </c>
+      <c r="K10" s="1">
+        <v>40</v>
+      </c>
+      <c r="L10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
         <v>34</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>147313</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3" t="s">
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11">
+        <v>79.05</v>
+      </c>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11">
+        <v>1.7</v>
+      </c>
+      <c r="I11" s="1">
+        <v>134.38</v>
+      </c>
+      <c r="J11">
+        <v>1.74</v>
+      </c>
+      <c r="K11" s="1">
+        <v>137.55</v>
+      </c>
+      <c r="L11" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="4" t="s">
+      <c r="D12" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12">
+        <v>50</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12">
+        <v>1.67</v>
+      </c>
+      <c r="I12" s="1">
+        <v>83.5</v>
+      </c>
+      <c r="J12">
+        <v>1.71</v>
+      </c>
+      <c r="K12" s="1">
+        <v>85.5</v>
+      </c>
+      <c r="L12" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="E13" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="G13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13">
+        <v>26.83</v>
+      </c>
+      <c r="I13" s="1">
+        <v>53.66</v>
+      </c>
+      <c r="J13">
+        <v>26.83</v>
+      </c>
+      <c r="K13" s="1">
+        <v>53.66</v>
+      </c>
+      <c r="L13" t="s">
+        <v>60</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>40</v>
+      </c>
+      <c r="E14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14">
+        <v>85.01000000000001</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14">
+        <v>1.67</v>
+      </c>
+      <c r="I14" s="1">
+        <v>141.97</v>
+      </c>
+      <c r="J14">
+        <v>1.71</v>
+      </c>
+      <c r="K14" s="1">
+        <v>145.37</v>
+      </c>
+      <c r="L14" t="s">
+        <v>61</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15">
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15">
+        <v>1.67</v>
+      </c>
+      <c r="I15" s="1">
+        <v>135.27</v>
+      </c>
+      <c r="J15">
+        <v>1.71</v>
+      </c>
+      <c r="K15" s="1">
+        <v>138.51</v>
+      </c>
+      <c r="L15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s">
+        <v>47</v>
+      </c>
+      <c r="H16">
+        <v>1.53</v>
+      </c>
+      <c r="I16" s="1">
+        <v>122.4</v>
+      </c>
+      <c r="J16">
+        <v>1.57</v>
+      </c>
+      <c r="K16" s="1">
+        <v>125.6</v>
+      </c>
+      <c r="L16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17">
+        <v>1.53</v>
+      </c>
+      <c r="I17" s="1">
+        <v>15.3</v>
+      </c>
+      <c r="J17">
+        <v>1.57</v>
+      </c>
+      <c r="K17" s="1">
+        <v>15.7</v>
+      </c>
+      <c r="L17" t="s">
+        <v>64</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="6">
-        <v>184.23</v>
-      </c>
-      <c r="C12" s="6">
-        <v>3</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.75</v>
-      </c>
-      <c r="E12" s="6">
-        <v>322.4</v>
-      </c>
-      <c r="F12" s="6">
-        <v>329.77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="6">
-        <v>127.59</v>
-      </c>
-      <c r="C13" s="6">
-        <v>3</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.4962</v>
-      </c>
-      <c r="E13" s="6">
-        <v>190.9</v>
-      </c>
-      <c r="F13" s="6">
-        <v>196.01</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="9">
-        <v>311.82</v>
-      </c>
-      <c r="C14" s="9">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>513.3</v>
-      </c>
-      <c r="F14" s="9">
-        <v>525.78</v>
+      <c r="E18" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18">
+        <v>42.02</v>
+      </c>
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18">
+        <v>1.66</v>
+      </c>
+      <c r="I18" s="1">
+        <v>69.75</v>
+      </c>
+      <c r="J18">
+        <v>1.7</v>
+      </c>
+      <c r="K18" s="1">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="L18" t="s">
+        <v>65</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="6">
+        <v>710.1799999999999</v>
+      </c>
+      <c r="C23" s="6">
+        <v>11</v>
+      </c>
+      <c r="D23" s="7">
+        <v>1.703</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1209.43</v>
+      </c>
+      <c r="F23" s="6">
+        <v>1237.84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B24" s="6">
+        <v>217.59</v>
+      </c>
+      <c r="C24" s="6">
+        <v>5</v>
+      </c>
+      <c r="D24" s="7">
+        <v>1.5102</v>
+      </c>
+      <c r="E24" s="6">
+        <v>328.6</v>
+      </c>
+      <c r="F24" s="6">
+        <v>337.31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="6">
+        <v>2</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
+      <c r="D25" s="7">
+        <v>26.83</v>
+      </c>
+      <c r="E25" s="6">
+        <v>53.66</v>
+      </c>
+      <c r="F25" s="6">
+        <v>53.66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B26" s="9">
+        <v>929.77</v>
+      </c>
+      <c r="C26" s="9">
+        <v>17</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="9">
+        <v>1591.69</v>
+      </c>
+      <c r="F26" s="9">
+        <v>1628.81</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
@@ -316,7 +316,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,12 +326,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,17 +375,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="112">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-01</t>
   </si>
   <si>
@@ -94,33 +103,42 @@
     <t>2026-06-25</t>
   </si>
   <si>
-    <t>Пловдив Цариградско шосе</t>
-  </si>
-  <si>
-    <t>Пловдив Бялата воденица</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>Тракия Езеро</t>
-  </si>
-  <si>
-    <t>АМ Тракия</t>
-  </si>
-  <si>
-    <t>Пловдив В. Априлов</t>
-  </si>
-  <si>
-    <t>Асеновград</t>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>2026-06-30</t>
+  </si>
+  <si>
+    <t>1144 Пловдив Стамболийски</t>
+  </si>
+  <si>
+    <t>1907 О5 Пловдив</t>
+  </si>
+  <si>
+    <t>1911 O5 Варна</t>
+  </si>
+  <si>
+    <t>1195 243 Тракия Езеро</t>
+  </si>
+  <si>
+    <t>1925 HW Trakia, 243 km. Sofia direc</t>
+  </si>
+  <si>
+    <t>1106 Пловдив В. Априлов</t>
+  </si>
+  <si>
+    <t>1119 Асеновград</t>
+  </si>
+  <si>
+    <t>1130 Пловдив Кукленско шосе</t>
+  </si>
+  <si>
+    <t>АУ3</t>
   </si>
   <si>
     <t>АУ10</t>
   </si>
   <si>
-    <t>АУ3</t>
-  </si>
-  <si>
     <t>АУ2</t>
   </si>
   <si>
@@ -139,12 +157,12 @@
     <t>АУ9</t>
   </si>
   <si>
+    <t>78970151027720112</t>
+  </si>
+  <si>
     <t>78970151027720187</t>
   </si>
   <si>
-    <t>78970151027720112</t>
-  </si>
-  <si>
     <t>78970151027720104</t>
   </si>
   <si>
@@ -169,70 +187,151 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-06-01 15:06:38</t>
-  </si>
-  <si>
-    <t>2026-06-01 15:50:26</t>
-  </si>
-  <si>
-    <t>2026-06-02 13:17:57</t>
-  </si>
-  <si>
-    <t>2026-06-02 14:42:37</t>
-  </si>
-  <si>
-    <t>2026-06-03 14:56:33</t>
-  </si>
-  <si>
-    <t>2026-06-04 08:36:45</t>
-  </si>
-  <si>
-    <t>2026-06-04 13:56:39</t>
-  </si>
-  <si>
-    <t>2026-06-05 10:30:26</t>
-  </si>
-  <si>
-    <t>2026-06-06 12:45:26</t>
-  </si>
-  <si>
-    <t>2026-06-08 11:50:04</t>
-  </si>
-  <si>
-    <t>2026-06-10 16:42:46</t>
-  </si>
-  <si>
-    <t>2026-06-11 12:17:00</t>
-  </si>
-  <si>
-    <t>2026-06-12 09:28:37</t>
-  </si>
-  <si>
-    <t>2026-06-12 09:41:52</t>
-  </si>
-  <si>
-    <t>2026-06-12 11:33:41</t>
-  </si>
-  <si>
-    <t>2026-06-16 10:18:09</t>
-  </si>
-  <si>
-    <t>2026-06-19 11:46:42</t>
-  </si>
-  <si>
-    <t>2026-06-22 10:41:52</t>
-  </si>
-  <si>
-    <t>2026-06-23 09:43:04</t>
-  </si>
-  <si>
-    <t>2026-06-23 16:03:12</t>
-  </si>
-  <si>
-    <t>2026-06-25 09:49:51</t>
-  </si>
-  <si>
-    <t>2026-06-25 14:34:04</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:49:00</t>
+  </si>
+  <si>
+    <t>15:06:00</t>
+  </si>
+  <si>
+    <t>13:18:00</t>
+  </si>
+  <si>
+    <t>14:42:00</t>
+  </si>
+  <si>
+    <t>14:56:00</t>
+  </si>
+  <si>
+    <t>08:36:00</t>
+  </si>
+  <si>
+    <t>13:56:00</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>12:45:00</t>
+  </si>
+  <si>
+    <t>11:49:00</t>
+  </si>
+  <si>
+    <t>16:42:00</t>
+  </si>
+  <si>
+    <t>12:17:00</t>
+  </si>
+  <si>
+    <t>09:41:00</t>
+  </si>
+  <si>
+    <t>09:28:00</t>
+  </si>
+  <si>
+    <t>11:33:00</t>
+  </si>
+  <si>
+    <t>10:18:00</t>
+  </si>
+  <si>
+    <t>11:47:00</t>
+  </si>
+  <si>
+    <t>10:42:00</t>
+  </si>
+  <si>
+    <t>16:08:00</t>
+  </si>
+  <si>
+    <t>09:43:00</t>
+  </si>
+  <si>
+    <t>09:50:00</t>
+  </si>
+  <si>
+    <t>14:34:00</t>
+  </si>
+  <si>
+    <t>09:18:00</t>
+  </si>
+  <si>
+    <t>15:04:00</t>
+  </si>
+  <si>
+    <t>3232706548 3232706548</t>
+  </si>
+  <si>
+    <t>3232728364 3232728364</t>
+  </si>
+  <si>
+    <t>3232771124 3232771124</t>
+  </si>
+  <si>
+    <t>3232742476 3232742476</t>
+  </si>
+  <si>
+    <t>3232811568 3232811568</t>
+  </si>
+  <si>
+    <t>3232862013 3232862013</t>
+  </si>
+  <si>
+    <t>3232862961 3232862961</t>
+  </si>
+  <si>
+    <t>3232897160 3232897160</t>
+  </si>
+  <si>
+    <t>3232961777 3232961777</t>
+  </si>
+  <si>
+    <t>3233060721 3233060721</t>
+  </si>
+  <si>
+    <t>3233153759 3233153759</t>
+  </si>
+  <si>
+    <t>3233200239 3233200239</t>
+  </si>
+  <si>
+    <t>3233252679 3233252679</t>
+  </si>
+  <si>
+    <t>3233255325 3233255325</t>
+  </si>
+  <si>
+    <t>3233258087 3233258087</t>
+  </si>
+  <si>
+    <t>3233444515 3233444515</t>
+  </si>
+  <si>
+    <t>3233587937 3233587937</t>
+  </si>
+  <si>
+    <t>3233721225 3233721225</t>
+  </si>
+  <si>
+    <t>3233775234 3233775234</t>
+  </si>
+  <si>
+    <t>3233770366 3233770366</t>
+  </si>
+  <si>
+    <t>3233862886 3233862886</t>
+  </si>
+  <si>
+    <t>3233869118 3233869118</t>
+  </si>
+  <si>
+    <t>3234060878 3234060878</t>
+  </si>
+  <si>
+    <t>3234113517 3234113517</t>
   </si>
   <si>
     <t>Общи литри по продукт / АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ</t>
@@ -650,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -659,14 +758,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -700,868 +802,1163 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2">
+        <v>48.42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2">
+        <v>1.65</v>
+      </c>
+      <c r="I2" s="1">
+        <v>79.89</v>
+      </c>
+      <c r="J2">
+        <v>1.69</v>
+      </c>
+      <c r="K2" s="1">
+        <v>81.83</v>
+      </c>
+      <c r="L2" t="s">
+        <v>58</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3">
+        <v>24.18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3">
+        <v>1.64</v>
+      </c>
+      <c r="I3" s="1">
+        <v>39.66</v>
+      </c>
+      <c r="J3">
+        <v>1.68</v>
+      </c>
+      <c r="K3" s="1">
+        <v>40.62</v>
+      </c>
+      <c r="L3" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
         <v>41</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D4" t="s">
         <v>49</v>
       </c>
-      <c r="F2">
-        <v>24.18</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.64</v>
-      </c>
-      <c r="H2">
-        <v>39.66</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="J2">
-        <v>40.62</v>
-      </c>
-      <c r="K2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F3">
-        <v>48.42</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.65</v>
-      </c>
-      <c r="H3">
-        <v>79.89</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.69</v>
-      </c>
-      <c r="J3">
-        <v>81.83</v>
-      </c>
-      <c r="K3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s">
-        <v>43</v>
-      </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F4">
         <v>9.130000000000001</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4">
         <v>1.53</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>13.97</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.57</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>14.33</v>
       </c>
-      <c r="K4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>60</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F5">
         <v>59</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5">
         <v>1.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>97.34999999999999</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.69</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>99.70999999999999</v>
       </c>
-      <c r="K5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="L5" t="s">
+        <v>61</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F6">
         <v>65.01000000000001</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6">
         <v>1.64</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>106.62</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.68</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>109.22</v>
       </c>
-      <c r="K6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F7">
         <v>27</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7">
         <v>1.53</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>41.31</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.57</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>42.39</v>
       </c>
-      <c r="K7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F8">
         <v>23.47</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8">
         <v>1.61</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>37.79</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.65</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>38.73</v>
       </c>
-      <c r="K8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="L8" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F9">
         <v>60.88</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9">
         <v>1.64</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="1">
         <v>99.84</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>1.68</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>102.28</v>
       </c>
-      <c r="K9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="L9" t="s">
+        <v>65</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F10">
         <v>56</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10">
         <v>1.62</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="1">
         <v>90.72</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>1.66</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>92.95999999999999</v>
       </c>
-      <c r="K10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="L10" t="s">
+        <v>66</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F11">
         <v>93.04000000000001</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11">
         <v>1.59</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="1">
         <v>147.93</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>1.63</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>151.66</v>
       </c>
-      <c r="K11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="L11" t="s">
+        <v>67</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F12">
         <v>63.01</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12">
         <v>1.58</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="1">
         <v>99.56</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12">
         <v>1.62</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="1">
         <v>102.08</v>
       </c>
-      <c r="K12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="L12" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13">
+        <v>57</v>
+      </c>
+      <c r="G13" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13">
+        <v>1.58</v>
+      </c>
+      <c r="I13" s="1">
+        <v>90.06</v>
+      </c>
+      <c r="J13">
+        <v>1.62</v>
+      </c>
+      <c r="K13" s="1">
+        <v>92.34</v>
+      </c>
+      <c r="L13" t="s">
+        <v>69</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+      <c r="H14">
+        <v>1.56</v>
+      </c>
+      <c r="I14" s="1">
+        <v>104.54</v>
+      </c>
+      <c r="J14">
+        <v>1.6</v>
+      </c>
+      <c r="K14" s="1">
+        <v>107.22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
         <v>41</v>
       </c>
-      <c r="E13" t="s">
+      <c r="D15" t="s">
         <v>49</v>
       </c>
-      <c r="F13">
-        <v>57</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1.58</v>
-      </c>
-      <c r="H13">
-        <v>90.06</v>
-      </c>
-      <c r="I13" s="1">
-        <v>1.62</v>
-      </c>
-      <c r="J13">
-        <v>92.34</v>
-      </c>
-      <c r="K13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14">
+      <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15">
         <v>72.98</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G15" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15">
         <v>1.56</v>
       </c>
-      <c r="H14">
+      <c r="I15" s="1">
         <v>113.85</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J15">
         <v>1.6</v>
       </c>
-      <c r="J14">
+      <c r="K15" s="1">
         <v>116.77</v>
       </c>
-      <c r="K14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15">
-        <v>67.01000000000001</v>
-      </c>
-      <c r="G15" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="H15">
-        <v>104.54</v>
-      </c>
-      <c r="I15" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="J15">
-        <v>107.22</v>
-      </c>
-      <c r="K15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="L15" t="s">
+        <v>71</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E16" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F16">
         <v>85</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16">
         <v>1.56</v>
       </c>
-      <c r="H16">
+      <c r="I16" s="1">
         <v>132.6</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16">
         <v>1.6</v>
       </c>
-      <c r="J16">
+      <c r="K16" s="1">
         <v>136</v>
       </c>
-      <c r="K16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="L16" t="s">
+        <v>72</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F17">
         <v>20.78</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17">
         <v>1.52</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="1">
         <v>31.59</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>1.56</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>32.42</v>
       </c>
-      <c r="K17" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+      <c r="L17" t="s">
+        <v>73</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E18" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F18">
         <v>75</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18">
         <v>1.51</v>
       </c>
-      <c r="H18">
+      <c r="I18" s="1">
         <v>113.25</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18">
         <v>1.55</v>
       </c>
-      <c r="J18">
+      <c r="K18" s="1">
         <v>116.25</v>
       </c>
-      <c r="K18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+      <c r="L18" t="s">
+        <v>74</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E19" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F19">
         <v>43.3</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19">
         <v>1.48</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="1">
         <v>64.08</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19">
         <v>1.52</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="1">
         <v>65.81999999999999</v>
       </c>
-      <c r="K19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="L19" t="s">
+        <v>75</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F20">
-        <v>80</v>
-      </c>
-      <c r="G20" s="1">
-        <v>1.46</v>
+        <v>90</v>
+      </c>
+      <c r="G20" t="s">
+        <v>57</v>
       </c>
       <c r="H20">
-        <v>116.8</v>
+        <v>1.48</v>
       </c>
       <c r="I20" s="1">
-        <v>1.5</v>
+        <v>133.2</v>
       </c>
       <c r="J20">
-        <v>120</v>
-      </c>
-      <c r="K20" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>1.52</v>
+      </c>
+      <c r="K20" s="1">
+        <v>136.8</v>
+      </c>
+      <c r="L20" t="s">
+        <v>76</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
         <v>32</v>
       </c>
       <c r="C21" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E21" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F21">
-        <v>90</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1.48</v>
+        <v>80</v>
+      </c>
+      <c r="G21" t="s">
+        <v>57</v>
       </c>
       <c r="H21">
-        <v>133.2</v>
+        <v>1.46</v>
       </c>
       <c r="I21" s="1">
-        <v>1.52</v>
+        <v>116.8</v>
       </c>
       <c r="J21">
-        <v>136.8</v>
-      </c>
-      <c r="K21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>1.5</v>
+      </c>
+      <c r="K21" s="1">
+        <v>120</v>
+      </c>
+      <c r="L21" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F22">
         <v>50</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22">
         <v>1.46</v>
       </c>
-      <c r="H22">
+      <c r="I22" s="1">
         <v>73</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22">
         <v>1.5</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="1">
         <v>75</v>
       </c>
-      <c r="K22" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="L22" t="s">
+        <v>78</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D23" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F23">
         <v>82.01000000000001</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23">
         <v>1.46</v>
       </c>
-      <c r="H23">
+      <c r="I23" s="1">
         <v>119.73</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23">
         <v>1.5</v>
       </c>
-      <c r="J23">
+      <c r="K23" s="1">
         <v>123.02</v>
       </c>
-      <c r="K23" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" s="6">
-        <v>1115.31</v>
-      </c>
-      <c r="C28" s="6">
-        <v>18</v>
-      </c>
-      <c r="D28" s="7">
-        <v>1.5634</v>
-      </c>
-      <c r="E28" s="6">
-        <v>1743.67</v>
-      </c>
-      <c r="F28" s="6">
-        <v>1788.31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="6">
+      <c r="L23" t="s">
+        <v>79</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>39</v>
+      </c>
+      <c r="D24" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24">
+        <v>42.44</v>
+      </c>
+      <c r="G24" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24">
+        <v>1.47</v>
+      </c>
+      <c r="I24" s="1">
+        <v>62.39</v>
+      </c>
+      <c r="J24">
+        <v>1.51</v>
+      </c>
+      <c r="K24" s="1">
+        <v>64.08</v>
+      </c>
+      <c r="L24" t="s">
+        <v>80</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25">
+        <v>50.01</v>
+      </c>
+      <c r="G25" t="s">
+        <v>57</v>
+      </c>
+      <c r="H25">
+        <v>1.46</v>
+      </c>
+      <c r="I25" s="1">
+        <v>73.01000000000001</v>
+      </c>
+      <c r="J25">
+        <v>1.5</v>
+      </c>
+      <c r="K25" s="1">
+        <v>75.02</v>
+      </c>
+      <c r="L25" t="s">
+        <v>81</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="6">
+        <v>1207.76</v>
+      </c>
+      <c r="C30" s="6">
+        <v>20</v>
+      </c>
+      <c r="D30" s="7">
+        <v>1.5558</v>
+      </c>
+      <c r="E30" s="6">
+        <v>1879.07</v>
+      </c>
+      <c r="F30" s="6">
+        <v>1927.41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="6">
         <v>136.91</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C31" s="6">
         <v>4</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D31" s="7">
         <v>1.4876</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E31" s="6">
         <v>203.67</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F31" s="6">
         <v>209.14</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="B30" s="9">
-        <v>1252.22</v>
-      </c>
-      <c r="C30" s="9">
-        <v>22</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="9">
-        <v>1947.34</v>
-      </c>
-      <c r="F30" s="9">
-        <v>1997.45</v>
+    <row r="32" spans="1:14">
+      <c r="A32" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="9">
+        <v>1344.67</v>
+      </c>
+      <c r="C32" s="9">
+        <v>24</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="9">
+        <v>2082.74</v>
+      </c>
+      <c r="F32" s="9">
+        <v>2136.55</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A28:F28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="76">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-03</t>
   </si>
   <si>
@@ -64,10 +70,34 @@
     <t>2026-07-14</t>
   </si>
   <si>
-    <t>Пловдив Цариградско шосе</t>
-  </si>
-  <si>
-    <t>Пловдив Кукленско шосе</t>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-24</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>1907 О5 Пловдив</t>
+  </si>
+  <si>
+    <t>1130 Пловдив Кукленско шосе</t>
   </si>
   <si>
     <t>АУ4</t>
@@ -76,12 +106,12 @@
     <t>АУ9</t>
   </si>
   <si>
+    <t>АУ3</t>
+  </si>
+  <si>
     <t>АУ10</t>
   </si>
   <si>
-    <t>АУ3</t>
-  </si>
-  <si>
     <t>АУ2</t>
   </si>
   <si>
@@ -94,12 +124,12 @@
     <t>78970151027720179</t>
   </si>
   <si>
+    <t>78970151027720112</t>
+  </si>
+  <si>
     <t>78970151027720187</t>
   </si>
   <si>
-    <t>78970151027720112</t>
-  </si>
-  <si>
     <t>78970151027720104</t>
   </si>
   <si>
@@ -112,22 +142,88 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-03 12:34:00</t>
-  </si>
-  <si>
-    <t>2026-07-06 09:47:29</t>
-  </si>
-  <si>
-    <t>2026-07-10 13:10:29</t>
-  </si>
-  <si>
-    <t>2026-07-10 13:38:49</t>
-  </si>
-  <si>
-    <t>2026-07-14 09:15:52</t>
-  </si>
-  <si>
-    <t>2026-07-14 11:08:15</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>12:33:00</t>
+  </si>
+  <si>
+    <t>09:47:00</t>
+  </si>
+  <si>
+    <t>13:39:00</t>
+  </si>
+  <si>
+    <t>13:10:00</t>
+  </si>
+  <si>
+    <t>09:15:00</t>
+  </si>
+  <si>
+    <t>11:08:00</t>
+  </si>
+  <si>
+    <t>12:17:00</t>
+  </si>
+  <si>
+    <t>11:15:00</t>
+  </si>
+  <si>
+    <t>08:51:00</t>
+  </si>
+  <si>
+    <t>09:40:00</t>
+  </si>
+  <si>
+    <t>09:18:00</t>
+  </si>
+  <si>
+    <t>12:14:00</t>
+  </si>
+  <si>
+    <t>16:37:00</t>
+  </si>
+  <si>
+    <t>3234238348 3234238348</t>
+  </si>
+  <si>
+    <t>3234401588 3234401588</t>
+  </si>
+  <si>
+    <t>3234640645 3234640645</t>
+  </si>
+  <si>
+    <t>3234638109 3234638109</t>
+  </si>
+  <si>
+    <t>3234794651 3234794651</t>
+  </si>
+  <si>
+    <t>3234796944 3234796944</t>
+  </si>
+  <si>
+    <t>3234895477 3234895477</t>
+  </si>
+  <si>
+    <t>3234953360 3234953360</t>
+  </si>
+  <si>
+    <t>3235099756 3235099756</t>
+  </si>
+  <si>
+    <t>3235146962 3235146962</t>
+  </si>
+  <si>
+    <t>3235301754 3235301754</t>
+  </si>
+  <si>
+    <t>3235439388 3235439388</t>
+  </si>
+  <si>
+    <t>3235592443 3235592443</t>
+  </si>
+  <si>
+    <t>3235658721 3235658721</t>
   </si>
   <si>
     <t>Общи литри по продукт / АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ</t>
@@ -545,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -554,15 +650,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -599,326 +697,720 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F2">
         <v>64</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2">
         <v>1.46</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>93.44</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.5</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>96</v>
       </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>30.03</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3">
         <v>1.47</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>44.14</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.51</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>45.35</v>
       </c>
-      <c r="K3" t="s">
-        <v>33</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4">
+        <v>46</v>
+      </c>
+      <c r="G4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4">
+        <v>1.5</v>
+      </c>
+      <c r="I4" s="1">
+        <v>69</v>
+      </c>
+      <c r="J4">
+        <v>1.54</v>
+      </c>
+      <c r="K4" s="1">
+        <v>70.84</v>
+      </c>
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B5" t="s">
         <v>26</v>
       </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4">
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5">
         <v>36.89</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H5">
         <v>1.49</v>
       </c>
-      <c r="H4">
+      <c r="I5" s="1">
         <v>54.97</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J5">
         <v>1.53</v>
       </c>
-      <c r="J4">
+      <c r="K5" s="1">
         <v>56.44</v>
       </c>
-      <c r="K4" t="s">
-        <v>34</v>
-      </c>
-      <c r="L4">
+      <c r="L5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="N5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>46</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="H5">
-        <v>69</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="J5">
-        <v>70.84</v>
-      </c>
-      <c r="K5" t="s">
-        <v>35</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>65.45</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6">
         <v>1.51</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>98.83</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.55</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>101.45</v>
       </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="N6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>79.98999999999999</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7">
         <v>1.44</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>115.19</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.48</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>118.39</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8">
+        <v>75.01000000000001</v>
+      </c>
+      <c r="G8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H8">
+        <v>1.56</v>
+      </c>
+      <c r="I8" s="1">
+        <v>117.02</v>
+      </c>
+      <c r="J8">
+        <v>1.6</v>
+      </c>
+      <c r="K8" s="1">
+        <v>120.02</v>
+      </c>
+      <c r="L8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9">
+        <v>1.46</v>
+      </c>
+      <c r="I9" s="1">
+        <v>27.74</v>
+      </c>
+      <c r="J9">
+        <v>1.5</v>
+      </c>
+      <c r="K9" s="1">
+        <v>28.5</v>
+      </c>
+      <c r="L9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10">
+        <v>45.35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H10">
+        <v>1.64</v>
+      </c>
+      <c r="I10" s="1">
+        <v>74.37</v>
+      </c>
+      <c r="J10">
+        <v>1.68</v>
+      </c>
+      <c r="K10" s="1">
+        <v>76.19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10">
+        <v>2818058</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11">
+        <v>1.63</v>
+      </c>
+      <c r="I11" s="1">
+        <v>65.2</v>
+      </c>
+      <c r="J11">
+        <v>1.67</v>
+      </c>
+      <c r="K11" s="1">
+        <v>66.8</v>
+      </c>
+      <c r="L11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12">
+        <v>62.01</v>
+      </c>
+      <c r="G12" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12">
+        <v>1.67</v>
+      </c>
+      <c r="I12" s="1">
+        <v>103.56</v>
+      </c>
+      <c r="J12">
+        <v>1.71</v>
+      </c>
+      <c r="K12" s="1">
+        <v>106.04</v>
+      </c>
+      <c r="L12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" t="s">
         <v>37</v>
       </c>
-      <c r="L7">
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+      <c r="F13">
+        <v>51.42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13">
+        <v>1.71</v>
+      </c>
+      <c r="I13" s="1">
+        <v>87.93000000000001</v>
+      </c>
+      <c r="J13">
+        <v>1.75</v>
+      </c>
+      <c r="K13" s="1">
+        <v>89.98</v>
+      </c>
+      <c r="L13" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="N13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="F14">
+        <v>52</v>
+      </c>
+      <c r="G14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14">
+        <v>1.71</v>
+      </c>
+      <c r="I14" s="1">
+        <v>88.92</v>
+      </c>
+      <c r="J14">
+        <v>1.75</v>
+      </c>
+      <c r="K14" s="1">
+        <v>91</v>
+      </c>
+      <c r="L14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15">
+        <v>31</v>
+      </c>
+      <c r="G15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15">
+        <v>1.73</v>
+      </c>
+      <c r="I15" s="1">
+        <v>53.63</v>
+      </c>
+      <c r="J15">
+        <v>1.77</v>
+      </c>
+      <c r="K15" s="1">
+        <v>54.87</v>
+      </c>
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6">
+        <v>599.16</v>
+      </c>
+      <c r="C20" s="6">
+        <v>12</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.5872</v>
+      </c>
+      <c r="E20" s="6">
+        <v>951.01</v>
+      </c>
+      <c r="F20" s="6">
+        <v>974.98</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="6">
-        <v>242.37</v>
-      </c>
-      <c r="C12" s="6">
-        <v>5</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.4869</v>
-      </c>
-      <c r="E12" s="6">
-        <v>360.38</v>
-      </c>
-      <c r="F12" s="6">
-        <v>370.08</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B13" s="6">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.4401</v>
-      </c>
-      <c r="E13" s="6">
-        <v>115.19</v>
-      </c>
-      <c r="F13" s="6">
-        <v>118.39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="9">
-        <v>322.36</v>
-      </c>
-      <c r="C14" s="9">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>475.57</v>
-      </c>
-      <c r="F14" s="9">
-        <v>488.47</v>
+      <c r="B21" s="6">
+        <v>98.98999999999999</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1.4439</v>
+      </c>
+      <c r="E21" s="6">
+        <v>142.93</v>
+      </c>
+      <c r="F21" s="6">
+        <v>146.89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="9">
+        <v>698.15</v>
+      </c>
+      <c r="C22" s="9">
+        <v>14</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="9">
+        <v>1093.94</v>
+      </c>
+      <c r="F22" s="9">
+        <v>1121.87</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
@@ -250,7 +250,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1361,7 +1361,7 @@
         <v>12</v>
       </c>
       <c r="D20" s="7">
-        <v>1.5872</v>
+        <v>1.587239</v>
       </c>
       <c r="E20" s="6">
         <v>951.01</v>
@@ -1381,7 +1381,7 @@
         <v>2</v>
       </c>
       <c r="D21" s="7">
-        <v>1.4439</v>
+        <v>1.443883</v>
       </c>
       <c r="E21" s="6">
         <v>142.93</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="77">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -641,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -654,13 +657,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -703,626 +706,671 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F2">
         <v>64</v>
       </c>
       <c r="G2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.46</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>93.44</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.5</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>96</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F3">
+        <v>30.033</v>
+      </c>
+      <c r="G3" t="s">
         <v>43</v>
       </c>
-      <c r="M2">
+      <c r="H3">
+        <v>1.406</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.47</v>
+      </c>
+      <c r="J3">
+        <v>44.14851</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L3" s="1">
+        <v>45.34983</v>
+      </c>
+      <c r="M3" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3">
-        <v>30.03</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="H3">
-        <v>1.47</v>
-      </c>
-      <c r="I3" s="1">
-        <v>44.14</v>
-      </c>
-      <c r="J3">
-        <v>1.51</v>
-      </c>
-      <c r="K3" s="1">
-        <v>45.35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F4">
         <v>46</v>
       </c>
       <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4">
+        <v>1.437</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="J4">
+        <v>69</v>
+      </c>
+      <c r="K4" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L4" s="1">
+        <v>70.84</v>
+      </c>
+      <c r="M4" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5">
+        <v>36.889</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="H5">
+        <v>1.437</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.49</v>
+      </c>
+      <c r="J5">
+        <v>54.96461</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="L5" s="1">
+        <v>56.44017</v>
+      </c>
+      <c r="M5" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6">
+        <v>65.452</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="H6">
+        <v>1.469</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J6">
+        <v>98.83252</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L6" s="1">
+        <v>101.4506</v>
+      </c>
+      <c r="M6" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
         <v>42</v>
       </c>
-      <c r="H4">
-        <v>1.5</v>
-      </c>
-      <c r="I4" s="1">
-        <v>69</v>
-      </c>
-      <c r="J4">
-        <v>1.54</v>
-      </c>
-      <c r="K4" s="1">
-        <v>70.84</v>
-      </c>
-      <c r="L4" t="s">
-        <v>45</v>
-      </c>
-      <c r="M4">
+      <c r="F7">
+        <v>79.99299999999999</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7">
+        <v>1.369</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.44</v>
+      </c>
+      <c r="J7">
+        <v>115.18992</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.48</v>
+      </c>
+      <c r="L7" s="1">
+        <v>118.38964</v>
+      </c>
+      <c r="M7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F5">
-        <v>36.89</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="O7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8">
+        <v>75.01300000000001</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8">
+        <v>1.499</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J8">
+        <v>117.02028</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="L8" s="1">
+        <v>120.0208</v>
+      </c>
+      <c r="M8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" t="s">
         <v>42</v>
-      </c>
-      <c r="H5">
-        <v>1.49</v>
-      </c>
-      <c r="I5" s="1">
-        <v>54.97</v>
-      </c>
-      <c r="J5">
-        <v>1.53</v>
-      </c>
-      <c r="K5" s="1">
-        <v>56.44</v>
-      </c>
-      <c r="L5" t="s">
-        <v>46</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E6" t="s">
-        <v>40</v>
-      </c>
-      <c r="F6">
-        <v>65.45</v>
-      </c>
-      <c r="G6" t="s">
-        <v>42</v>
-      </c>
-      <c r="H6">
-        <v>1.51</v>
-      </c>
-      <c r="I6" s="1">
-        <v>98.83</v>
-      </c>
-      <c r="J6">
-        <v>1.55</v>
-      </c>
-      <c r="K6" s="1">
-        <v>101.45</v>
-      </c>
-      <c r="L6" t="s">
-        <v>47</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="G7" t="s">
-        <v>42</v>
-      </c>
-      <c r="H7">
-        <v>1.44</v>
-      </c>
-      <c r="I7" s="1">
-        <v>115.19</v>
-      </c>
-      <c r="J7">
-        <v>1.48</v>
-      </c>
-      <c r="K7" s="1">
-        <v>118.39</v>
-      </c>
-      <c r="L7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8">
-        <v>75.01000000000001</v>
-      </c>
-      <c r="G8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H8">
-        <v>1.56</v>
-      </c>
-      <c r="I8" s="1">
-        <v>117.02</v>
-      </c>
-      <c r="J8">
-        <v>1.6</v>
-      </c>
-      <c r="K8" s="1">
-        <v>120.02</v>
-      </c>
-      <c r="L8" t="s">
-        <v>49</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>41</v>
       </c>
       <c r="F9">
         <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H9">
+        <v>1.369</v>
+      </c>
+      <c r="I9" s="1">
         <v>1.46</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9">
         <v>27.74</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="1">
         <v>1.5</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>28.5</v>
       </c>
-      <c r="L9" t="s">
-        <v>50</v>
-      </c>
-      <c r="M9">
+      <c r="M9" t="s">
+        <v>51</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10">
+        <v>45.351</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H10">
+        <v>1.546</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="J10">
+        <v>74.37564</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L10" s="1">
+        <v>76.18968</v>
+      </c>
+      <c r="M10" t="s">
+        <v>52</v>
+      </c>
+      <c r="N10">
+        <v>2818058</v>
+      </c>
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>27</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10">
-        <v>45.35</v>
-      </c>
-      <c r="G10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10">
-        <v>1.64</v>
-      </c>
-      <c r="I10" s="1">
-        <v>74.37</v>
-      </c>
-      <c r="J10">
-        <v>1.68</v>
-      </c>
-      <c r="K10" s="1">
-        <v>76.19</v>
-      </c>
-      <c r="L10" t="s">
-        <v>51</v>
-      </c>
-      <c r="M10">
-        <v>2818058</v>
-      </c>
-      <c r="N10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>35</v>
-      </c>
       <c r="E11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F11">
         <v>40</v>
       </c>
       <c r="G11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H11">
+        <v>1.564</v>
+      </c>
+      <c r="I11" s="1">
         <v>1.63</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11">
         <v>65.2</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="1">
         <v>1.67</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>66.8</v>
       </c>
-      <c r="L11" t="s">
-        <v>52</v>
-      </c>
-      <c r="M11">
+      <c r="M11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12">
+        <v>62.012</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12">
+        <v>1.619</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.67</v>
+      </c>
+      <c r="J12">
+        <v>103.56004</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1.71</v>
+      </c>
+      <c r="L12" s="1">
+        <v>106.04052</v>
+      </c>
+      <c r="M12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
       </c>
-      <c r="D12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12">
-        <v>62.01</v>
-      </c>
-      <c r="G12" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12">
-        <v>1.67</v>
-      </c>
-      <c r="I12" s="1">
-        <v>103.56</v>
-      </c>
-      <c r="J12">
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13">
+        <v>51.423</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13">
+        <v>1.619</v>
+      </c>
+      <c r="I13" s="1">
         <v>1.71</v>
       </c>
-      <c r="K12" s="1">
-        <v>106.04</v>
-      </c>
-      <c r="L12" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12">
+      <c r="J13">
+        <v>87.93333</v>
+      </c>
+      <c r="K13" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L13" s="1">
+        <v>89.99025</v>
+      </c>
+      <c r="M13" t="s">
+        <v>54</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="O13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
         <v>27</v>
       </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" t="s">
-        <v>40</v>
-      </c>
-      <c r="F13">
-        <v>51.42</v>
-      </c>
-      <c r="G13" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13">
-        <v>1.71</v>
-      </c>
-      <c r="I13" s="1">
-        <v>87.93000000000001</v>
-      </c>
-      <c r="J13">
-        <v>1.75</v>
-      </c>
-      <c r="K13" s="1">
-        <v>89.98</v>
-      </c>
-      <c r="L13" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
       <c r="C14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14">
         <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H14">
+        <v>1.674</v>
+      </c>
+      <c r="I14" s="1">
         <v>1.71</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14">
         <v>88.92</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>1.75</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>91</v>
       </c>
-      <c r="L14" t="s">
-        <v>54</v>
-      </c>
-      <c r="M14">
+      <c r="M14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
-      <c r="N14" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15">
         <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H15">
+        <v>1.689</v>
+      </c>
+      <c r="I15" s="1">
         <v>1.73</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15">
         <v>53.63</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="1">
         <v>1.77</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>54.87</v>
       </c>
-      <c r="L15" t="s">
-        <v>55</v>
-      </c>
-      <c r="M15">
+      <c r="M15" t="s">
+        <v>56</v>
+      </c>
+      <c r="N15">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>69</v>
+      <c r="O15" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1332,56 +1380,56 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B20" s="6">
-        <v>599.16</v>
+        <v>599.173</v>
       </c>
       <c r="C20" s="6">
         <v>12</v>
       </c>
       <c r="D20" s="7">
-        <v>1.587239</v>
+        <v>1.587229</v>
       </c>
       <c r="E20" s="6">
-        <v>951.01</v>
+        <v>951.02</v>
       </c>
       <c r="F20" s="6">
-        <v>974.98</v>
+        <v>974.99</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="6">
-        <v>98.98999999999999</v>
+        <v>98.99299999999999</v>
       </c>
       <c r="C21" s="6">
         <v>2</v>
       </c>
       <c r="D21" s="7">
-        <v>1.443883</v>
+        <v>1.443839</v>
       </c>
       <c r="E21" s="6">
         <v>142.93</v>
@@ -1392,20 +1440,20 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="9">
-        <v>698.15</v>
+        <v>698.1660000000001</v>
       </c>
       <c r="C22" s="9">
         <v>14</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="9">
-        <v>1093.94</v>
+        <v>1093.95</v>
       </c>
       <c r="F22" s="9">
-        <v>1121.87</v>
+        <v>1121.88</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="76">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -252,8 +249,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -346,10 +343,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -644,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -657,13 +654,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -706,671 +703,626 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F2">
         <v>64</v>
       </c>
       <c r="G2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2">
+        <v>1.46</v>
+      </c>
+      <c r="I2" s="1">
+        <v>93.44</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>96</v>
+      </c>
+      <c r="L2" t="s">
         <v>43</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.46</v>
-      </c>
-      <c r="J2">
-        <v>93.44</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>96</v>
-      </c>
-      <c r="M2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F3">
         <v>30.033</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H3">
-        <v>1.406</v>
+        <v>1.47</v>
       </c>
       <c r="I3" s="1">
-        <v>1.47</v>
+        <v>44.149</v>
       </c>
       <c r="J3">
-        <v>44.14851</v>
+        <v>1.51</v>
       </c>
       <c r="K3" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L3" s="1">
-        <v>45.34983</v>
-      </c>
-      <c r="M3" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3">
+        <v>45.35</v>
+      </c>
+      <c r="L3" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F4">
         <v>46</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H4">
-        <v>1.437</v>
+        <v>1.5</v>
       </c>
       <c r="I4" s="1">
-        <v>1.5</v>
+        <v>69</v>
       </c>
       <c r="J4">
-        <v>69</v>
+        <v>1.54</v>
       </c>
       <c r="K4" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L4" s="1">
         <v>70.84</v>
       </c>
-      <c r="M4" t="s">
-        <v>46</v>
-      </c>
-      <c r="N4">
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>36.889</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H5">
-        <v>1.437</v>
+        <v>1.49</v>
       </c>
       <c r="I5" s="1">
-        <v>1.49</v>
+        <v>54.965</v>
       </c>
       <c r="J5">
-        <v>54.96461</v>
+        <v>1.53</v>
       </c>
       <c r="K5" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="L5" s="1">
-        <v>56.44017</v>
-      </c>
-      <c r="M5" t="s">
-        <v>47</v>
-      </c>
-      <c r="N5">
+        <v>56.44</v>
+      </c>
+      <c r="L5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F6">
         <v>65.452</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H6">
-        <v>1.469</v>
+        <v>1.51</v>
       </c>
       <c r="I6" s="1">
-        <v>1.51</v>
+        <v>98.833</v>
       </c>
       <c r="J6">
-        <v>98.83252</v>
+        <v>1.55</v>
       </c>
       <c r="K6" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L6" s="1">
-        <v>101.4506</v>
-      </c>
-      <c r="M6" t="s">
-        <v>48</v>
-      </c>
-      <c r="N6">
+        <v>101.451</v>
+      </c>
+      <c r="L6" t="s">
+        <v>47</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>79.99299999999999</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H7">
-        <v>1.369</v>
+        <v>1.44</v>
       </c>
       <c r="I7" s="1">
-        <v>1.44</v>
+        <v>115.19</v>
       </c>
       <c r="J7">
-        <v>115.18992</v>
+        <v>1.48</v>
       </c>
       <c r="K7" s="1">
-        <v>1.48</v>
-      </c>
-      <c r="L7" s="1">
-        <v>118.38964</v>
-      </c>
-      <c r="M7" t="s">
-        <v>49</v>
-      </c>
-      <c r="N7">
+        <v>118.39</v>
+      </c>
+      <c r="L7" t="s">
+        <v>48</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F8">
         <v>75.01300000000001</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H8">
-        <v>1.499</v>
+        <v>1.56</v>
       </c>
       <c r="I8" s="1">
-        <v>1.56</v>
+        <v>117.02</v>
       </c>
       <c r="J8">
-        <v>117.02028</v>
+        <v>1.6</v>
       </c>
       <c r="K8" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="L8" s="1">
-        <v>120.0208</v>
-      </c>
-      <c r="M8" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8">
+        <v>120.021</v>
+      </c>
+      <c r="L8" t="s">
+        <v>49</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9">
         <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H9">
-        <v>1.369</v>
+        <v>1.46</v>
       </c>
       <c r="I9" s="1">
-        <v>1.46</v>
+        <v>27.74</v>
       </c>
       <c r="J9">
-        <v>27.74</v>
+        <v>1.5</v>
       </c>
       <c r="K9" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L9" s="1">
         <v>28.5</v>
       </c>
-      <c r="M9" t="s">
-        <v>51</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10">
         <v>45.351</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H10">
-        <v>1.546</v>
+        <v>1.64</v>
       </c>
       <c r="I10" s="1">
-        <v>1.64</v>
+        <v>74.376</v>
       </c>
       <c r="J10">
-        <v>74.37564</v>
+        <v>1.68</v>
       </c>
       <c r="K10" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L10" s="1">
-        <v>76.18968</v>
-      </c>
-      <c r="M10" t="s">
-        <v>52</v>
-      </c>
-      <c r="N10">
+        <v>76.19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>51</v>
+      </c>
+      <c r="M10">
         <v>2818058</v>
       </c>
-      <c r="O10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11">
         <v>40</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H11">
-        <v>1.564</v>
+        <v>1.63</v>
       </c>
       <c r="I11" s="1">
-        <v>1.63</v>
+        <v>65.2</v>
       </c>
       <c r="J11">
-        <v>65.2</v>
+        <v>1.67</v>
       </c>
       <c r="K11" s="1">
-        <v>1.67</v>
-      </c>
-      <c r="L11" s="1">
         <v>66.8</v>
       </c>
-      <c r="M11" t="s">
-        <v>53</v>
-      </c>
-      <c r="N11">
+      <c r="L11" t="s">
+        <v>52</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F12">
         <v>62.012</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H12">
-        <v>1.619</v>
+        <v>1.67</v>
       </c>
       <c r="I12" s="1">
-        <v>1.67</v>
+        <v>103.56</v>
       </c>
       <c r="J12">
-        <v>103.56004</v>
+        <v>1.71</v>
       </c>
       <c r="K12" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="L12" s="1">
-        <v>106.04052</v>
-      </c>
-      <c r="M12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N12">
+        <v>106.041</v>
+      </c>
+      <c r="L12" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
-      <c r="O12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F13">
         <v>51.423</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H13">
-        <v>1.619</v>
+        <v>1.71</v>
       </c>
       <c r="I13" s="1">
-        <v>1.71</v>
+        <v>87.93300000000001</v>
       </c>
       <c r="J13">
-        <v>87.93333</v>
+        <v>1.75</v>
       </c>
       <c r="K13" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L13" s="1">
-        <v>89.99025</v>
-      </c>
-      <c r="M13" t="s">
-        <v>54</v>
-      </c>
-      <c r="N13">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="L13" t="s">
+        <v>53</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-      <c r="O13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F14">
         <v>52</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H14">
-        <v>1.674</v>
+        <v>1.71</v>
       </c>
       <c r="I14" s="1">
-        <v>1.71</v>
+        <v>88.92</v>
       </c>
       <c r="J14">
-        <v>88.92</v>
+        <v>1.75</v>
       </c>
       <c r="K14" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L14" s="1">
         <v>91</v>
       </c>
-      <c r="M14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N14">
+      <c r="L14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14">
         <v>0</v>
       </c>
-      <c r="O14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="N14" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s">
         <v>26</v>
       </c>
-      <c r="B15" t="s">
-        <v>27</v>
-      </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F15">
         <v>31</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H15">
-        <v>1.689</v>
+        <v>1.73</v>
       </c>
       <c r="I15" s="1">
-        <v>1.73</v>
+        <v>53.63</v>
       </c>
       <c r="J15">
-        <v>53.63</v>
+        <v>1.77</v>
       </c>
       <c r="K15" s="1">
-        <v>1.77</v>
-      </c>
-      <c r="L15" s="1">
         <v>54.87</v>
       </c>
-      <c r="M15" t="s">
-        <v>56</v>
-      </c>
-      <c r="N15">
+      <c r="L15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M15">
         <v>0</v>
       </c>
-      <c r="O15" t="s">
-        <v>70</v>
+      <c r="N15" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1380,67 +1332,67 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="E19" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6">
         <v>599.173</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="7">
         <v>12</v>
       </c>
       <c r="D20" s="7">
-        <v>1.587229</v>
-      </c>
-      <c r="E20" s="6">
-        <v>951.02</v>
-      </c>
-      <c r="F20" s="6">
-        <v>974.99</v>
+        <v>1.587</v>
+      </c>
+      <c r="E20" s="7">
+        <v>951.026</v>
+      </c>
+      <c r="F20" s="7">
+        <v>974.9930000000001</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6">
         <v>98.99299999999999</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="7">
         <v>2</v>
       </c>
       <c r="D21" s="7">
-        <v>1.443839</v>
-      </c>
-      <c r="E21" s="6">
+        <v>1.444</v>
+      </c>
+      <c r="E21" s="7">
         <v>142.93</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="7">
         <v>146.89</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="9">
         <v>698.1660000000001</v>
@@ -1450,10 +1402,10 @@
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="9">
-        <v>1093.95</v>
+        <v>1093.956</v>
       </c>
       <c r="F22" s="9">
-        <v>1121.88</v>
+        <v>1121.883</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ/АГРАРЕН УНИВЕРСИТЕТ - ПЛОВДИВ.xlsx
@@ -619,10 +619,10 @@
         <v>26</v>
       </c>
       <c r="H2" s="1">
-        <v>1.429</v>
+        <v>1.51</v>
       </c>
       <c r="I2" s="1">
-        <v>114.32</v>
+        <v>120.8</v>
       </c>
       <c r="J2" s="1">
         <v>1.55</v>
@@ -663,10 +663,10 @@
         <v>26</v>
       </c>
       <c r="H3" s="1">
-        <v>1.709</v>
+        <v>1.8</v>
       </c>
       <c r="I3" s="1">
-        <v>157.228</v>
+        <v>165.6</v>
       </c>
       <c r="J3" s="1">
         <v>1.84</v>
@@ -707,10 +707,10 @@
         <v>26</v>
       </c>
       <c r="H4" s="1">
-        <v>1.709</v>
+        <v>1.78</v>
       </c>
       <c r="I4" s="1">
-        <v>66.66800000000001</v>
+        <v>69.438</v>
       </c>
       <c r="J4" s="1">
         <v>1.82</v>
@@ -769,10 +769,10 @@
         <v>2</v>
       </c>
       <c r="D9" s="8">
-        <v>1.709</v>
+        <v>1.79405</v>
       </c>
       <c r="E9" s="6">
-        <v>223.9</v>
+        <v>235.04</v>
       </c>
       <c r="F9" s="6">
         <v>240.28</v>
@@ -789,10 +789,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="8">
-        <v>1.429</v>
+        <v>1.51</v>
       </c>
       <c r="E10" s="6">
-        <v>114.32</v>
+        <v>120.8</v>
       </c>
       <c r="F10" s="6">
         <v>124</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="10">
-        <v>338.22</v>
+        <v>355.84</v>
       </c>
       <c r="F11" s="10">
         <v>364.28</v>
